--- a/Validations_07082026.xlsx
+++ b/Validations_07082026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OmnIQConsulting\OmniFlow\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6C1FEF6-671B-4691-A7CC-C9A26E922446}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F627E25C-9FA0-4DE6-A232-EE4EDD94F943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="6" activeTab="13" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Setup Page" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="49">
   <si>
     <t>Data privacy</t>
   </si>
@@ -59,21 +59,6 @@
   </si>
   <si>
     <t>Multi Tenancy</t>
-  </si>
-  <si>
-    <t>SKU Code</t>
-  </si>
-  <si>
-    <t>1. Flag ++</t>
-  </si>
-  <si>
-    <t>2. Auto acknowledge</t>
-  </si>
-  <si>
-    <t>3. Notification that comment is also added</t>
-  </si>
-  <si>
-    <t>4. Mark done - verification - option to add comment</t>
   </si>
   <si>
     <t>1. When we click on confirm import after validating any bulk import file - there is no way we can track the progress, we don't really know if the uploading is working or not</t>
@@ -263,7 +248,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -275,7 +260,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -420,6 +404,50 @@
         <a:xfrm>
           <a:off x="12115800" y="10454640"/>
           <a:ext cx="3168433" cy="3436620"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>541020</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>138072</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>28</xdr:col>
+      <xdr:colOff>350520</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>77509</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="Picture 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EFC18D3C-DEB8-E77E-4D4B-19DB58B11C1E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="15171420" y="3978552"/>
+          <a:ext cx="2247900" cy="2499757"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -748,7 +776,7 @@
   <sheetData>
     <row r="2" spans="2:2" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B2" s="5" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="2:2" x14ac:dyDescent="0.3">
@@ -756,227 +784,227 @@
     </row>
     <row r="4" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
     </row>
     <row r="11" spans="2:2" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B11" s="5" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
     <row r="14" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B14" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B15" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B16" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B17" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
     </row>
     <row r="18" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B18" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="19" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B19" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
     </row>
     <row r="20" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B20" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="23" spans="2:2" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B23" s="5" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
     </row>
     <row r="26" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B26" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="27" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B27" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="28" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B28" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="29" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B29" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
     </row>
     <row r="30" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B30" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="31" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B31" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
     </row>
     <row r="32" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B32" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
     </row>
     <row r="33" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B33" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
     </row>
     <row r="35" spans="2:2" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B35" s="5" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
     </row>
     <row r="38" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B38" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="39" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B39" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="40" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B40" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="41" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B41" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="44" spans="2:2" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B44" s="5" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
     </row>
     <row r="47" spans="2:2" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B47" s="5" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
     </row>
     <row r="50" spans="2:2" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B50" s="5" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
     </row>
     <row r="52" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B52" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
     </row>
     <row r="53" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B53" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
     </row>
     <row r="54" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B54" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
     </row>
     <row r="56" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B56" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
     </row>
     <row r="57" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B57" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
     </row>
     <row r="58" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B58" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
     </row>
     <row r="59" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B59" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
     </row>
     <row r="60" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B60" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="61" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B61" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
     </row>
     <row r="65" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B65" s="1" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
     </row>
     <row r="66" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B66" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
     </row>
     <row r="67" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B67" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
     </row>
     <row r="68" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B68" s="7" t="s">
-        <v>46</v>
+      <c r="B68" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="69" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B69" s="7" t="s">
-        <v>47</v>
+      <c r="B69" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="70" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B70" s="7" t="s">
-        <v>48</v>
+      <c r="B70" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="71" spans="2:2" x14ac:dyDescent="0.3">
@@ -999,25 +1027,25 @@
     </row>
     <row r="78" spans="2:2" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B78" s="5" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
     </row>
     <row r="81" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B81" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
     </row>
     <row r="84" spans="2:4" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B84" s="5" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
     </row>
     <row r="86" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B86" s="8" t="s">
-        <v>50</v>
-      </c>
-      <c r="C86" s="8"/>
-      <c r="D86" s="8"/>
+      <c r="B86" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="C86" s="7"/>
+      <c r="D86" s="7"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1083,22 +1111,22 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="2" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B2" s="7" t="s">
+      <c r="B2" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="3" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B3" s="7" t="s">
+      <c r="B3" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="4" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B4" s="7" t="s">
+      <c r="B4" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="5" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B5" s="7" t="s">
+      <c r="B5" t="s">
         <v>5</v>
       </c>
     </row>
@@ -1126,22 +1154,22 @@
   <sheetData>
     <row r="2" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B2" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
     </row>
     <row r="4" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="13" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B13" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
     </row>
   </sheetData>
@@ -1161,28 +1189,17 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37617031-97A4-415F-BDE0-490229B4C280}">
-  <dimension ref="B4:B8"/>
+  <dimension ref="B4:B6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="4" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B4" s="3" t="s">
-        <v>8</v>
-      </c>
+      <c r="B4" s="3"/>
     </row>
     <row r="5" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B5" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="7" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B7" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="8" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B8" s="3" t="s">
-        <v>11</v>
-      </c>
+      <c r="B5" s="3"/>
+    </row>
+    <row r="6" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B6" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1195,14 +1212,10 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="4" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B4" s="3" t="s">
-        <v>8</v>
-      </c>
+      <c r="B4" s="3"/>
     </row>
     <row r="5" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B5" s="3" t="s">
-        <v>9</v>
-      </c>
+      <c r="B5" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1215,14 +1228,10 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1" s="3" t="s">
-        <v>8</v>
-      </c>
+      <c r="A1" s="3"/>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A2" s="3" t="s">
-        <v>9</v>
-      </c>
+      <c r="A2" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1253,9 +1262,7 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="2" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B2" s="1" t="s">
-        <v>7</v>
-      </c>
+      <c r="B2" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
